--- a/autoast/jobs_to_fail_FAST.xlsx
+++ b/autoast/jobs_to_fail_FAST.xlsx
@@ -781,7 +781,7 @@
       </c>
       <c r="H5" s="1" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="I5" s="1" t="inlineStr">

--- a/autoast/jobs_to_fail_FAST.xlsx
+++ b/autoast/jobs_to_fail_FAST.xlsx
@@ -781,7 +781,7 @@
       </c>
       <c r="H5" s="1" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="I5" s="1" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
-          <t>Requeued</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="N6" s="3" t="n">
